--- a/cypress/resultados/reportes_pruebas_control_horario.xlsx
+++ b/cypress/resultados/reportes_pruebas_control_horario.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -806,9 +806,38 @@
         <v/>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Empleados_20260127080614027</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Empleados</v>
+      </c>
+      <c r="C15" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-01-27 08:06:14</v>
+      </c>
+      <c r="E15" t="str">
+        <v>OK</v>
+      </c>
+      <c r="F15" t="str">
+        <v>TC001 - Cargar la pantalla correctamente</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Comportamiento correcto</v>
+      </c>
+      <c r="H15" t="str">
+        <v>Comportamiento correcto</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/cypress/resultados/reportes_pruebas_control_horario.xlsx
+++ b/cypress/resultados/reportes_pruebas_control_horario.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -835,9 +835,38 @@
         <v/>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Empleados_20260211112058648</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Empleados</v>
+      </c>
+      <c r="C16" t="str">
+        <v>TC001</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-02-11 11:20:58</v>
+      </c>
+      <c r="E16" t="str">
+        <v>OK</v>
+      </c>
+      <c r="F16" t="str">
+        <v xml:space="preserve">TC001 - </v>
+      </c>
+      <c r="G16" t="str">
+        <v>Comportamiento correcto</v>
+      </c>
+      <c r="H16" t="str">
+        <v>Comportamiento correcto</v>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I16"/>
   </ignoredErrors>
 </worksheet>
 </file>
